--- a/ABB_Proyecto/01_Ofertas/Ofertas.xlsx
+++ b/ABB_Proyecto/01_Ofertas/Ofertas.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
